--- a/progLinear/exercicios/Simplex_duas_fases_1.xlsx
+++ b/progLinear/exercicios/Simplex_duas_fases_1.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30524"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/29EF9A7B83F2DDC4/Arquivo_pessoal/Ensino/programacao-linear/"/>
@@ -176,7 +176,7 @@
     <definedName name="solver_ver" localSheetId="1" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -202,19 +202,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="63">
   <si>
-    <t>x2</t>
+    <t>x</t>
   </si>
   <si>
-    <t>x1</t>
-  </si>
-  <si>
-    <t>x3</t>
+    <t>y</t>
   </si>
   <si>
     <t>bi</t>
-  </si>
-  <si>
-    <t>Zi</t>
   </si>
   <si>
     <t>Restrições</t>
@@ -223,16 +217,25 @@
     <t>Função objetivo</t>
   </si>
   <si>
-    <t>Z</t>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>C2</t>
   </si>
   <si>
     <t>Coeficientes</t>
   </si>
   <si>
-    <t>C1</t>
+    <t>Z</t>
   </si>
   <si>
-    <t>C2</t>
+    <t>n=</t>
+  </si>
+  <si>
+    <t>m=</t>
+  </si>
+  <si>
+    <t>FASE 1: CRIAÇÃO DAS VARIÁVEIS DE EXCESSO E ARTIFICIAIS; DEFINIÇÃO DA SOLUÇÃO BASE PARA A FUNÇÃO OBJETIVO ARTIFICAL</t>
   </si>
   <si>
     <t>Quadro 0</t>
@@ -241,31 +244,13 @@
     <t>Base</t>
   </si>
   <si>
-    <t>m=</t>
-  </si>
-  <si>
-    <t>n=</t>
-  </si>
-  <si>
-    <t>Quadro 1</t>
-  </si>
-  <si>
-    <t>razão</t>
-  </si>
-  <si>
-    <t>Quadro 2</t>
-  </si>
-  <si>
-    <t>C3</t>
-  </si>
-  <si>
-    <t>Quadro 3</t>
-  </si>
-  <si>
     <t>e1</t>
   </si>
   <si>
     <t>e2</t>
+  </si>
+  <si>
+    <t>e3</t>
   </si>
   <si>
     <t>a1</t>
@@ -274,28 +259,58 @@
     <t>a2</t>
   </si>
   <si>
+    <t>a3</t>
+  </si>
+  <si>
+    <t>razão</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>Zi</t>
+  </si>
+  <si>
     <t>Cai-Zai</t>
   </si>
   <si>
-    <t>L2'=L2/3</t>
+    <t>Quadro 1</t>
   </si>
   <si>
-    <t>L1'=-L2'+L1</t>
+    <t>L1'=L1/3</t>
   </si>
   <si>
-    <t>L1'=L1/8</t>
+    <t>L2'=-L1'+L2</t>
   </si>
   <si>
-    <t>L2'=-L1'*4+L2</t>
+    <t>L3'+-L1'+L3</t>
   </si>
   <si>
-    <t>L2'=L2/4</t>
+    <t>Quadro 2</t>
   </si>
   <si>
-    <t>L1'=-L2'*0,5+L2</t>
+    <t>L1'+-L3'*$e38+e38</t>
   </si>
   <si>
-    <t>FASE 1: CRIAÇÃO DAS VARIÁVEIS DE EXCESSO E ARTIFICIAIS; DEFINIÇÃO DA SOLUÇÃO BASE PARA A FUNÇÃO OBJETIVO ARTIFICAL</t>
+    <t>L2'=-L3'*$e40+e40</t>
+  </si>
+  <si>
+    <t>L3'=L3/$e40</t>
+  </si>
+  <si>
+    <t>desconsiderar</t>
+  </si>
+  <si>
+    <t>Quadro 3</t>
+  </si>
+  <si>
+    <t>L1'=L2'/2+L1</t>
+  </si>
+  <si>
+    <t>L2'=L2/2,5</t>
+  </si>
+  <si>
+    <t>L3'=L2'*1,5+L3</t>
   </si>
   <si>
     <t>FASE 2: OBTENÇÃO DA SOLUÇÃO A PARTIR DA SOLUÇÃO BÁSICA ANTERIOR</t>
@@ -304,16 +319,40 @@
     <t>Zi-Ci</t>
   </si>
   <si>
-    <t>L1'=L1/0,75</t>
+    <t>x1</t>
   </si>
   <si>
-    <t>L2'=L1'/2+L2</t>
+    <t>x2</t>
+  </si>
+  <si>
+    <t>L1'=-2L2'+L1</t>
+  </si>
+  <si>
+    <t>L2'=L2/6</t>
+  </si>
+  <si>
+    <t>L1'=L1/$e34</t>
+  </si>
+  <si>
+    <t>L2'=-$e35*L1'+L2</t>
+  </si>
+  <si>
+    <t>L1'=L1/0,2</t>
+  </si>
+  <si>
+    <t>L2'=L2+0,2L1'</t>
+  </si>
+  <si>
+    <t>L1'=-L2'+L1</t>
+  </si>
+  <si>
+    <t>L2'=L2/3</t>
+  </si>
+  <si>
+    <t>L1'=-L2'*$e34+L1</t>
   </si>
   <si>
     <t>L2'=L2/$e35</t>
-  </si>
-  <si>
-    <t>L1'=-L2'*$e34+L1</t>
   </si>
   <si>
     <t>L1'=L1*2</t>
@@ -325,77 +364,38 @@
     <t>não participa</t>
   </si>
   <si>
+    <t>L1'=L1+L2'</t>
+  </si>
+  <si>
     <t>L2'=L2</t>
   </si>
   <si>
-    <t>L1'=L1+L2'</t>
+    <t>x3</t>
   </si>
   <si>
-    <t>L2'=L2/6</t>
+    <t>L1'=L1/8</t>
   </si>
   <si>
-    <t>L1'=L1/$e34</t>
+    <t>L2'=-L1'*4+L2</t>
   </si>
   <si>
-    <t>x</t>
+    <t>L1'=-L2'*0,5+L2</t>
   </si>
   <si>
-    <t>y</t>
+    <t>L2'=L2/4</t>
   </si>
   <si>
-    <t>L1'=-2L2'+L1</t>
+    <t>L1'=L1/0,75</t>
   </si>
   <si>
-    <t>L2'=-$e35*L1'+L2</t>
-  </si>
-  <si>
-    <t>desconsiderar</t>
-  </si>
-  <si>
-    <t>L1'=L1/0,2</t>
-  </si>
-  <si>
-    <t>L2'=L2+0,2L1'</t>
-  </si>
-  <si>
-    <t>a3</t>
-  </si>
-  <si>
-    <t>e3</t>
-  </si>
-  <si>
-    <t>L1'=L1/3</t>
-  </si>
-  <si>
-    <t>L2'=-L1'+L2</t>
-  </si>
-  <si>
-    <t>L3'+-L1'+L3</t>
-  </si>
-  <si>
-    <t>L3'=L3/$e40</t>
-  </si>
-  <si>
-    <t>L2'=-L3'*$e40+e40</t>
-  </si>
-  <si>
-    <t>L1'+-L3'*$e38+e38</t>
-  </si>
-  <si>
-    <t>L2'=L2/2,5</t>
-  </si>
-  <si>
-    <t>L3'=L2'*1,5+L3</t>
-  </si>
-  <si>
-    <t>L1'=L2'/2+L1</t>
+    <t>L2'=L1'/2+L2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -826,30 +826,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C327E972-55CF-458E-98E4-461FA823DE8F}">
   <dimension ref="A3:Q103"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="25.88671875" customWidth="1"/>
-    <col min="3" max="4" width="6.109375" customWidth="1"/>
+    <col min="1" max="1" width="25.85546875" customWidth="1"/>
+    <col min="3" max="4" width="6.140625" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="15" max="15" width="12.77734375" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6">
       <c r="B3" s="4" t="s">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="F3" s="4"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
       </c>
       <c r="B4" s="5">
         <v>1</v>
@@ -865,7 +865,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6">
       <c r="B5" s="5">
         <v>2</v>
       </c>
@@ -880,7 +880,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6">
       <c r="B6" s="5">
         <v>1</v>
       </c>
@@ -895,9 +895,9 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B8" s="5">
         <v>2.4</v>
@@ -906,17 +906,17 @@
         <v>3.1999999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6">
       <c r="B10" s="4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11" s="5">
         <v>3</v>
@@ -925,84 +925,84 @@
         <v>6</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F11" s="5">
         <f>SUMPRODUCT(B8:C8,B11:C11)</f>
         <v>26.4</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6">
       <c r="B14" s="3" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C14">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6">
       <c r="B15" s="3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6">
       <c r="B16" s="3"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15">
       <c r="A17" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B17" s="3"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15">
       <c r="A19" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
       <c r="B20" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="G20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="L20" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="O20" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H20" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L20" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="M20" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O20" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:15">
       <c r="B21" s="9" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D21" s="5">
         <v>0</v>
@@ -1039,12 +1039,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15">
       <c r="B22" s="9" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D22" s="5">
         <v>0</v>
@@ -1081,12 +1081,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15">
       <c r="B23" s="9" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D23" s="5">
         <v>0</v>
@@ -1123,9 +1123,9 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15">
       <c r="D24" s="7" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E24" s="10">
         <v>0</v>
@@ -1153,9 +1153,9 @@
       </c>
       <c r="M24" s="10"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15">
       <c r="D25" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E25" s="10">
         <v>4</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="M25" s="10"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15">
       <c r="D26" s="2"/>
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
@@ -1195,117 +1195,117 @@
       <c r="L26" s="11"/>
       <c r="M26" s="11"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15">
       <c r="D27" t="s">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="E27">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15">
       <c r="D28" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="E28">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15">
       <c r="D29" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15">
       <c r="D30" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E30">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15">
       <c r="D31" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="E31">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15">
       <c r="D32" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E32">
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17">
       <c r="D33" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E33">
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17">
       <c r="D34" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="E34">
         <v>5.5</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17">
       <c r="A36" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17">
+      <c r="B37" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H37" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B37" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H37" s="4" t="s">
-        <v>21</v>
-      </c>
       <c r="I37" s="4" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="M37" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O37" s="4"/>
       <c r="Q37" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17">
       <c r="B38" s="9" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D38" s="5">
         <v>5</v>
@@ -1347,19 +1347,19 @@
         <v>4</v>
       </c>
       <c r="O38" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="Q38">
         <f>M38/E38</f>
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17">
       <c r="B39" s="9" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D39" s="5">
         <v>0</v>
@@ -1401,19 +1401,19 @@
         <v>4</v>
       </c>
       <c r="O39" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="Q39">
         <f>M39/E39</f>
         <v>2.4</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17">
       <c r="B40" s="9" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D40" s="5">
         <v>0</v>
@@ -1455,16 +1455,16 @@
         <v>1.5</v>
       </c>
       <c r="O40" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="Q40">
         <f>M40/E40</f>
         <v>2.2499999999999996</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17">
       <c r="D41" s="7" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E41" s="10">
         <f>$D38*E38+$D39*E39+$D40*E40</f>
@@ -1503,9 +1503,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17">
       <c r="D42" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E42" s="8">
         <f>4-E41</f>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="M42" s="10"/>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17">
       <c r="D43" s="2"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11"/>
@@ -1553,117 +1553,117 @@
       <c r="L43" s="11"/>
       <c r="M43" s="11"/>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17">
       <c r="D44" t="s">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="E44">
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17">
       <c r="D45" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="E45">
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17">
       <c r="D46" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E46">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17">
       <c r="D47" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E47">
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17">
       <c r="D48" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17">
       <c r="D49" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E49">
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17">
       <c r="D50" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E50">
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17">
       <c r="D51" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="E51">
         <v>1.5</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17">
       <c r="A54" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17">
+      <c r="B55" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J55" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B55" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F55" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="G55" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H55" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I55" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="J55" s="4" t="s">
-        <v>22</v>
-      </c>
       <c r="K55" s="4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="L55" s="4" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="M55" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O55" s="4"/>
       <c r="Q55" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17">
       <c r="B56" s="9" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D56" s="5">
         <v>5</v>
@@ -1705,19 +1705,19 @@
         <v>3.25</v>
       </c>
       <c r="O56" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="Q56">
         <f>M56/I56</f>
         <v>6.5000000000000018</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17">
       <c r="B57" s="9" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D57" s="5">
         <v>0</v>
@@ -1759,19 +1759,19 @@
         <v>0.25000000000000044</v>
       </c>
       <c r="O57" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="Q57">
         <f>M57/I57</f>
         <v>0.1000000000000002</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17">
       <c r="B58" s="9" t="s">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D58" s="5">
         <v>4</v>
@@ -1813,15 +1813,15 @@
         <v>2.2499999999999996</v>
       </c>
       <c r="O58" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="Q58" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17">
       <c r="D59" s="7" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E59" s="10">
         <f>$D56*E56+$D57*E57+$D58*E58</f>
@@ -1860,9 +1860,9 @@
         <v>25.25</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17">
       <c r="D60" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E60" s="10">
         <f>4-E59</f>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="M60" s="10"/>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17">
       <c r="D61" s="2"/>
       <c r="E61" s="11"/>
       <c r="F61" s="11"/>
@@ -1910,114 +1910,114 @@
       <c r="L61" s="11"/>
       <c r="M61" s="11"/>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17">
       <c r="D62" t="s">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="E62">
         <v>2.25</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17">
       <c r="D63" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="E63">
         <v>3.25</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17">
       <c r="D64" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E64">
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15">
       <c r="D65" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E65">
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15">
       <c r="D66" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="E66">
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15">
       <c r="D67" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E67">
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15">
       <c r="D68" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E68">
         <v>0.25</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15">
       <c r="D69" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="E69">
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15">
       <c r="A72" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15">
+      <c r="B73" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H73" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I73" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J73" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K73" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="L73" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B73" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E73" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F73" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="G73" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H73" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I73" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="J73" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K73" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L73" s="4" t="s">
-        <v>52</v>
-      </c>
       <c r="M73" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O73" s="4"/>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15">
       <c r="B74" s="9" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D74" s="5">
         <v>5</v>
@@ -2059,15 +2059,15 @@
         <v>3.1999999999999997</v>
       </c>
       <c r="O74" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15">
       <c r="B75" s="9" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D75" s="5">
         <v>-1</v>
@@ -2109,15 +2109,15 @@
         <v>0.10000000000000017</v>
       </c>
       <c r="O75" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15">
       <c r="B76" s="9" t="s">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D76" s="5">
         <v>4</v>
@@ -2159,12 +2159,12 @@
         <v>2.4</v>
       </c>
       <c r="O76" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15">
       <c r="D77" s="7" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E77" s="10">
         <f>D74*E74+D75*E75+D76*E76</f>
@@ -2203,9 +2203,9 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15">
       <c r="D78" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E78" s="10"/>
       <c r="F78" s="10"/>
@@ -2217,7 +2217,7 @@
       <c r="L78" s="10"/>
       <c r="M78" s="10"/>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15">
       <c r="D79" s="2"/>
       <c r="E79" s="11"/>
       <c r="F79" s="11"/>
@@ -2229,109 +2229,109 @@
       <c r="L79" s="11"/>
       <c r="M79" s="11"/>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15">
       <c r="D80" t="s">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="E80">
         <v>2.4</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10">
       <c r="D81" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="E81">
         <v>3.2</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10">
       <c r="D82" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E82">
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10">
       <c r="D83" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E83">
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10">
       <c r="D84" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="E84">
         <v>0.1</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10">
       <c r="D85" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E85">
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10">
       <c r="D86" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E86">
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10">
       <c r="D87" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="E87">
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10">
       <c r="A89" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10">
       <c r="A91" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10">
       <c r="B92" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="J92" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10">
       <c r="B93" s="9" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D93" s="5">
         <v>6</v>
@@ -2355,12 +2355,12 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10">
       <c r="B94" s="9" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D94" s="5">
         <v>0</v>
@@ -2384,12 +2384,12 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10">
       <c r="B95" s="9" t="s">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D95" s="5">
         <v>3</v>
@@ -2413,9 +2413,9 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10">
       <c r="D96" s="7" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E96" s="10">
         <f>D93*E93+D94*E94+D95*E95</f>
@@ -2442,9 +2442,9 @@
         <v>26.400000000000002</v>
       </c>
     </row>
-    <row r="97" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="97" spans="4:13">
       <c r="D97" s="2" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E97" s="10">
         <f>E96-3</f>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="J97" s="10"/>
     </row>
-    <row r="98" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="98" spans="4:13">
       <c r="D98" s="2"/>
       <c r="E98" s="11"/>
       <c r="F98" s="11"/>
@@ -2480,41 +2480,41 @@
       <c r="L98" s="11"/>
       <c r="M98" s="11"/>
     </row>
-    <row r="99" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="99" spans="4:13">
       <c r="D99" t="s">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="E99">
         <v>2.4</v>
       </c>
     </row>
-    <row r="100" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="100" spans="4:13">
       <c r="D100" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="E100">
         <v>3.2</v>
       </c>
     </row>
-    <row r="101" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="101" spans="4:13">
       <c r="D101" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E101">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="102" spans="4:13">
       <c r="D102" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E102">
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="103" spans="4:13">
       <c r="D103" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="E103">
         <v>0.1</v>
@@ -2528,30 +2528,30 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4C71E29-7FA4-4161-A4DB-33D82BCC3595}">
   <dimension ref="A3:O85"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="25.88671875" customWidth="1"/>
-    <col min="3" max="4" width="6.109375" customWidth="1"/>
+    <col min="1" max="1" width="25.85546875" customWidth="1"/>
+    <col min="3" max="4" width="6.140625" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="13" max="13" width="12.77734375" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6">
       <c r="B3" s="4" t="s">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="F3" s="4"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
       </c>
       <c r="B4" s="5">
         <v>2</v>
@@ -2567,7 +2567,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6">
       <c r="B5" s="5">
         <v>1</v>
       </c>
@@ -2582,9 +2582,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B7" s="5">
         <v>0</v>
@@ -2593,17 +2593,17 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6">
       <c r="B9" s="4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" s="5">
         <v>4</v>
@@ -2612,78 +2612,78 @@
         <v>1</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F10" s="5">
         <f>SUMPRODUCT(B7:C7,B10:C10)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6">
       <c r="B13" s="3" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C13">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6">
       <c r="B14" s="3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C14">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6">
       <c r="B15" s="3"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6">
       <c r="A16" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B16" s="3"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13">
       <c r="A18" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="B19" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="G19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="M19" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H19" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="M19" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:13">
       <c r="B20" s="9" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D20" s="5">
         <v>0</v>
@@ -2714,12 +2714,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13">
       <c r="B21" s="9" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D21" s="5">
         <v>0</v>
@@ -2750,11 +2750,11 @@
         <v>3.3333333333333335</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13">
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E22" s="5">
         <v>0</v>
@@ -2778,9 +2778,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13">
       <c r="D23" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E23" s="5">
         <v>3</v>
@@ -2802,94 +2802,94 @@
       </c>
       <c r="K23" s="5"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13">
       <c r="D25" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13">
       <c r="D26" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E26">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13">
       <c r="D27" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E27">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13">
       <c r="D28" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E28">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13">
       <c r="D29" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E29">
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13">
       <c r="D30" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E30">
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13">
       <c r="A32" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15">
+      <c r="B33" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H33" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B33" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="G33" s="4" t="s">
+      <c r="I33" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="O33" t="s">
         <v>20</v>
       </c>
-      <c r="H33" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J33" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K33" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O33" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:15">
       <c r="B34" s="9" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D34" s="5">
         <v>0</v>
@@ -2923,19 +2923,19 @@
         <v>3.333333333333333</v>
       </c>
       <c r="M34" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="O34">
         <f>K34/E34</f>
         <v>1.9999999999999998</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15">
       <c r="B35" s="9" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D35" s="5">
         <v>8</v>
@@ -2969,18 +2969,18 @@
         <v>3.3333333333333335</v>
       </c>
       <c r="M35" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O35">
         <f>K35/E35</f>
         <v>20.000000000000004</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15">
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
       <c r="D36" s="7" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E36" s="5">
         <f>SUMPRODUCT($D34:$D35,E34:E35)</f>
@@ -3011,9 +3011,9 @@
         <v>26.666666666666668</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15">
       <c r="D37" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E37" s="8">
         <f>3-E36</f>
@@ -3041,91 +3041,91 @@
       </c>
       <c r="K37" s="5"/>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15">
       <c r="D39" t="s">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="E39">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15">
       <c r="D40" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="E40">
         <v>3.33</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15">
       <c r="D41" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E41">
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15">
       <c r="D42" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E42">
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15">
       <c r="D43" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E43">
         <v>3.33</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15">
       <c r="D44" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E44">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15">
       <c r="A46" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15">
+      <c r="B47" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I47" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="B47" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="G47" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H47" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I47" s="4" t="s">
-        <v>22</v>
-      </c>
       <c r="J47" s="4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15">
       <c r="B48" s="9" t="s">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D48" s="5">
         <v>3</v>
@@ -3159,15 +3159,15 @@
         <v>1.9999999999999998</v>
       </c>
       <c r="M48" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13">
       <c r="B49" s="9" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D49" s="5">
         <v>8</v>
@@ -3201,14 +3201,14 @@
         <v>3</v>
       </c>
       <c r="M49" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13">
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
       <c r="D50" s="7" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E50" s="5">
         <f>SUMPRODUCT($D48:$D49,E48:E49)</f>
@@ -3239,9 +3239,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13">
       <c r="D51" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E51" s="5">
         <f>3-E50</f>
@@ -3269,93 +3269,93 @@
       </c>
       <c r="K51" s="5"/>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13">
       <c r="D53" t="s">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="E53">
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13">
       <c r="D54" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="E54">
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13">
       <c r="D55" t="s">
+        <v>14</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13">
+      <c r="D56" t="s">
+        <v>15</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13">
+      <c r="D57" t="s">
+        <v>17</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13">
+      <c r="D58" t="s">
+        <v>18</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13">
+      <c r="A61" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13">
+      <c r="A63" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13">
+      <c r="B64" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H64" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I64" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="K64" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="D56" t="s">
-        <v>21</v>
-      </c>
-      <c r="E56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="D57" t="s">
-        <v>22</v>
-      </c>
-      <c r="E57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="D58" t="s">
-        <v>23</v>
-      </c>
-      <c r="E58">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A61" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A63" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B64" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E64" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F64" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="G64" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H64" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I64" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="K64" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="65" spans="1:11">
       <c r="B65" s="9" t="s">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D65" s="5">
         <v>4</v>
@@ -3380,12 +3380,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11">
       <c r="B66" s="9" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D66" s="5">
         <v>1</v>
@@ -3406,11 +3406,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11">
       <c r="B67" s="7"/>
       <c r="C67" s="7"/>
       <c r="D67" s="7" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E67" s="5">
         <v>4</v>
@@ -3428,9 +3428,9 @@
       </c>
       <c r="I67" s="5"/>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11">
       <c r="D68" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E68" s="5">
         <f>E67-4</f>
@@ -3450,70 +3450,70 @@
       </c>
       <c r="I68" s="5"/>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11">
       <c r="D70" t="s">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="E70">
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11">
       <c r="D71" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="E71">
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11">
       <c r="D72" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E72">
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11">
       <c r="D73" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E73">
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11">
       <c r="A75" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11">
+      <c r="B76" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H76" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B76" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E76" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F76" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="G76" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H76" s="4" t="s">
-        <v>21</v>
-      </c>
       <c r="I76" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K76" s="4"/>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11">
       <c r="B77" s="9" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D77" s="5">
         <v>0</v>
@@ -3539,15 +3539,15 @@
         <v>10</v>
       </c>
       <c r="K77" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11">
       <c r="B78" s="9" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D78" s="5">
         <v>1</v>
@@ -3573,14 +3573,14 @@
         <v>5</v>
       </c>
       <c r="K78" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11">
       <c r="B79" s="7"/>
       <c r="C79" s="7"/>
       <c r="D79" s="7" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E79" s="5">
         <f>D77*E77+D78*E78</f>
@@ -3603,9 +3603,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11">
       <c r="D80" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E80" s="5">
         <f>E79-4</f>
@@ -3625,33 +3625,33 @@
       </c>
       <c r="I80" s="5"/>
     </row>
-    <row r="82" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="4:5">
       <c r="D82" t="s">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="E82">
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="4:5">
       <c r="D83" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="E83">
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="4:5">
       <c r="D84" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E84">
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="4:5">
       <c r="D85" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E85">
         <v>10</v>
@@ -3665,29 +3665,29 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4EB5291-EE6E-48B4-AC94-DCBA16921FF8}">
   <dimension ref="A3:P98"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="25.88671875" customWidth="1"/>
-    <col min="3" max="4" width="6.109375" customWidth="1"/>
+    <col min="1" max="1" width="25.85546875" customWidth="1"/>
+    <col min="3" max="4" width="6.140625" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6">
       <c r="B3" s="4" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="F3" s="4"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
       </c>
       <c r="B4" s="5">
         <v>1</v>
@@ -3703,7 +3703,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6">
       <c r="B5" s="5">
         <v>2</v>
       </c>
@@ -3718,9 +3718,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B7" s="5">
         <v>0</v>
@@ -3729,17 +3729,17 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6">
       <c r="B9" s="4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" s="5">
         <v>2</v>
@@ -3748,78 +3748,78 @@
         <v>1</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F10" s="5">
         <f>SUMPRODUCT(B7:C7,B10:C10)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6">
       <c r="B13" s="3" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C13">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6">
       <c r="B14" s="3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C14">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6">
       <c r="B15" s="3"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6">
       <c r="A16" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B16" s="3"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13">
       <c r="A18" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="B19" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="M19" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H19" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="M19" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:13">
       <c r="B20" s="9" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D20" s="5">
         <v>0</v>
@@ -3850,12 +3850,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13">
       <c r="B21" s="9" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D21" s="5">
         <v>0</v>
@@ -3886,11 +3886,11 @@
         <v>4.666666666666667</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13">
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E22" s="5">
         <v>0</v>
@@ -3914,9 +3914,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13">
       <c r="D23" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E23" s="5">
         <v>3</v>
@@ -3941,94 +3941,94 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13">
       <c r="D25" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13">
       <c r="D26" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E26">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13">
       <c r="D27" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E27">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13">
       <c r="D28" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E28">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13">
       <c r="D29" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E29">
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13">
       <c r="D30" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E30">
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13">
       <c r="A32" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16">
+      <c r="B33" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H33" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B33" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G33" s="4" t="s">
+      <c r="I33" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="O33" t="s">
         <v>20</v>
       </c>
-      <c r="H33" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J33" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K33" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O33" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:16">
       <c r="B34" s="9" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D34" s="5">
         <v>0</v>
@@ -4062,19 +4062,19 @@
         <v>5.333333333333333</v>
       </c>
       <c r="M34" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="O34">
         <f>K34/E34</f>
         <v>15.999999999999996</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16">
       <c r="B35" s="9" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D35" s="5">
         <v>4</v>
@@ -4108,18 +4108,18 @@
         <v>4.666666666666667</v>
       </c>
       <c r="M35" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="O35">
         <f>K35/E35</f>
         <v>7.0000000000000009</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16">
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
       <c r="D36" s="7" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E36" s="5">
         <f>D34*E34+D35*E35</f>
@@ -4150,9 +4150,9 @@
         <v>18.666666666666668</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16">
       <c r="D37" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E37" s="8">
         <f>3-E36</f>
@@ -4183,94 +4183,94 @@
         <v>5.3333333333333321</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16">
       <c r="D39" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="E39">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16">
       <c r="D40" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E40">
         <v>4.67</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16">
       <c r="D41" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E41">
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16">
       <c r="D42" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E42">
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16">
       <c r="D43" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E43">
         <v>5.33</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16">
       <c r="D44" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E44">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16">
       <c r="A46" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="B47" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I47" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B47" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G47" s="4" t="s">
+      <c r="J47" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="P47" t="s">
         <v>20</v>
       </c>
-      <c r="H47" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I47" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J47" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K47" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="P47" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="1:16">
       <c r="B48" s="9" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D48" s="5">
         <v>0</v>
@@ -4304,19 +4304,19 @@
         <v>2.9999999999999991</v>
       </c>
       <c r="M48" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="P48">
         <f>K48/H48</f>
         <v>5.9999999999999982</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:16">
       <c r="B49" s="9" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D49" s="5">
         <v>3</v>
@@ -4350,18 +4350,18 @@
         <v>7.0000000000000009</v>
       </c>
       <c r="M49" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="P49">
         <f>K49/H49</f>
         <v>-14.000000000000002</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:16">
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
       <c r="D50" s="7" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E50" s="5">
         <f>D48*E48+D49*E49</f>
@@ -4392,9 +4392,9 @@
         <v>21.000000000000004</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:16">
       <c r="D51" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E51" s="5">
         <f>3-E50</f>
@@ -4425,91 +4425,91 @@
         <v>2.9999999999999964</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:16">
       <c r="D53" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="E53">
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:16">
       <c r="D54" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E54">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:16">
       <c r="D55" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E55">
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:16">
       <c r="D56" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E56">
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:16">
       <c r="D57" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E57">
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:16">
       <c r="D58" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E58">
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:16">
       <c r="A60" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16">
       <c r="B61" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16">
       <c r="B62" s="9" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D62" s="5">
         <v>-1</v>
@@ -4543,15 +4543,15 @@
         <v>5.9999999999999982</v>
       </c>
       <c r="M62" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16">
       <c r="B63" s="9" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D63" s="5">
         <v>3</v>
@@ -4585,14 +4585,14 @@
         <v>10</v>
       </c>
       <c r="M63" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16">
       <c r="B64" s="7"/>
       <c r="C64" s="7"/>
       <c r="D64" s="7" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E64" s="5">
         <f>D62*E62+D63*E63</f>
@@ -4623,9 +4623,9 @@
         <v>24</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11">
       <c r="D65" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E65" s="5">
         <f>3-E64</f>
@@ -4656,93 +4656,93 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11">
       <c r="D67" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="E67">
         <v>10</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11">
       <c r="D68" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E68">
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11">
       <c r="D69" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E69">
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11">
       <c r="D70" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E70">
         <v>6</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11">
       <c r="D71" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E71">
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11">
       <c r="D72" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E72">
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11">
       <c r="A74" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11">
       <c r="A76" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11">
       <c r="B77" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G77" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H77" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I77" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="K77" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H77" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I77" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="K77" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="78" spans="1:11">
       <c r="B78" s="9" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D78" s="5">
         <v>0</v>
@@ -4763,15 +4763,15 @@
         <v>6</v>
       </c>
       <c r="K78" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11">
       <c r="B79" s="9" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D79" s="5">
         <v>2</v>
@@ -4796,11 +4796,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11">
       <c r="B80" s="7"/>
       <c r="C80" s="7"/>
       <c r="D80" s="7" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E80" s="5">
         <f>D78*E78+D79*E79</f>
@@ -4823,9 +4823,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:11">
       <c r="D81" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E81" s="5">
         <f>E80-2</f>
@@ -4845,70 +4845,70 @@
       </c>
       <c r="I81" s="5"/>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:11">
       <c r="D83" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="E83">
         <v>10</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11">
       <c r="D84" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E84">
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11">
       <c r="D85" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E85">
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11">
       <c r="D86" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E86">
         <v>6</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11">
       <c r="A88" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11">
+      <c r="B89" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G89" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H89" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B89" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E89" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="F89" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G89" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H89" s="4" t="s">
-        <v>21</v>
-      </c>
       <c r="I89" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K89" s="4"/>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:11">
       <c r="B90" s="9" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D90" s="5">
         <v>0</v>
@@ -4934,15 +4934,15 @@
         <v>16</v>
       </c>
       <c r="K90" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11">
       <c r="B91" s="9" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D91" s="5">
         <v>1</v>
@@ -4968,14 +4968,14 @@
         <v>10</v>
       </c>
       <c r="K91" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11">
       <c r="B92" s="7"/>
       <c r="C92" s="7"/>
       <c r="D92" s="7" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E92" s="5">
         <f>D90*E90+D91*E91</f>
@@ -4998,9 +4998,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:11">
       <c r="D93" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E93" s="5">
         <f>E92-2</f>
@@ -5020,33 +5020,33 @@
       </c>
       <c r="I93" s="5"/>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:11">
       <c r="D95" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="E95">
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:11">
       <c r="D96" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E96">
         <v>10</v>
       </c>
     </row>
-    <row r="97" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="4:5">
       <c r="D97" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E97">
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="4:5">
       <c r="D98" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E98">
         <v>16</v>
@@ -5060,32 +5060,32 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE0BD840-D73C-4E1B-8482-F70BBB5C96FD}">
   <dimension ref="A3:P89"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="25.88671875" customWidth="1"/>
-    <col min="3" max="4" width="6.109375" customWidth="1"/>
+    <col min="1" max="1" width="25.85546875" customWidth="1"/>
+    <col min="3" max="4" width="6.140625" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="B3" s="4" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="4"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="G3" s="4"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
       </c>
       <c r="B4" s="5">
         <v>8</v>
@@ -5104,7 +5104,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="B5" s="5">
         <v>4</v>
       </c>
@@ -5122,9 +5122,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B7" s="5">
         <v>0</v>
@@ -5136,20 +5136,20 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="B9" s="4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" s="5">
         <v>16</v>
@@ -5161,81 +5161,81 @@
         <v>5</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G10" s="5">
         <f>SUMPRODUCT(B7:D7,B10:D10)</f>
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="B13" s="3" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C13">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="B14" s="3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C14">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="B15" s="3"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B16" s="3"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14">
       <c r="A18" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="B19" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G19" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="L19" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="N19" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I19" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L19" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="N19" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:14">
       <c r="B20" s="9" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D20" s="5">
         <v>0</v>
@@ -5269,12 +5269,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14">
       <c r="B21" s="9" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D21" s="5">
         <v>0</v>
@@ -5308,11 +5308,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14">
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E22" s="5">
         <v>0</v>
@@ -5339,9 +5339,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14">
       <c r="D23" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E23" s="8">
         <v>12</v>
@@ -5368,105 +5368,105 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14">
       <c r="D25" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14">
       <c r="D26" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E26">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14">
       <c r="D27" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E27">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14">
       <c r="D28" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E28">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14">
       <c r="D29" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14">
       <c r="D30" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E30">
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14">
       <c r="D31" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E31">
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16">
       <c r="A33" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
+      <c r="B34" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I34" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B34" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G34" s="4" t="s">
+      <c r="J34" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="L34" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="H34" s="4" t="s">
+      <c r="P34" t="s">
         <v>20</v>
       </c>
-      <c r="I34" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J34" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K34" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L34" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="P34" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:16">
       <c r="B35" s="9" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D35" s="5">
         <v>12</v>
@@ -5504,19 +5504,19 @@
         <v>2</v>
       </c>
       <c r="N35" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="P35">
         <f>L35/F35</f>
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16">
       <c r="B36" s="9" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D36" s="5">
         <v>0</v>
@@ -5554,18 +5554,18 @@
         <v>4</v>
       </c>
       <c r="N36" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="P36">
         <f>L36/F36</f>
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16">
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
       <c r="D37" s="7" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E37" s="5">
         <f>D35*E35+D36*E36</f>
@@ -5600,9 +5600,9 @@
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16">
       <c r="D38" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E38" s="5">
         <f>12-E37</f>
@@ -5637,102 +5637,102 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16">
       <c r="D40" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="E40">
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16">
       <c r="D41" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E41">
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16">
       <c r="D42" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E42">
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16">
       <c r="D43" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E43">
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16">
       <c r="D44" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E44">
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16">
       <c r="D45" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E45">
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16">
       <c r="D46" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E46">
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16">
       <c r="A48" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
+      <c r="B49" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J49" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B49" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G49" s="4" t="s">
+      <c r="K49" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="L49" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="H49" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I49" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J49" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K49" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L49" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:14">
       <c r="B50" s="9" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D50" s="5">
         <v>12</v>
@@ -5770,15 +5770,15 @@
         <v>1.5</v>
       </c>
       <c r="N50" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14">
       <c r="B51" s="9" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D51" s="5">
         <v>10</v>
@@ -5816,14 +5816,14 @@
         <v>1</v>
       </c>
       <c r="N51" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
       <c r="D52" s="7" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E52" s="5">
         <f>D50*E50+D51*E51</f>
@@ -5858,9 +5858,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14">
       <c r="D53" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E53" s="5">
         <f>12-E52</f>
@@ -5895,104 +5895,104 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:14">
       <c r="D55" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="E55">
         <v>1.5</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:14">
       <c r="D56" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E56">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:14">
       <c r="D57" t="s">
+        <v>56</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14">
+      <c r="D58" t="s">
+        <v>14</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14">
+      <c r="D59" t="s">
+        <v>15</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14">
+      <c r="D60" t="s">
+        <v>17</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14">
+      <c r="D61" t="s">
+        <v>18</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14">
+      <c r="A63" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12">
+      <c r="A65" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12">
+      <c r="B66" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H66" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I66" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J66" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="D58" t="s">
+      <c r="L66" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E58">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="D59" t="s">
-        <v>21</v>
-      </c>
-      <c r="E59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="D60" t="s">
-        <v>22</v>
-      </c>
-      <c r="E60">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="D61" t="s">
-        <v>23</v>
-      </c>
-      <c r="E61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A65" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B66" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E66" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="F66" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G66" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="H66" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I66" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J66" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="L66" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="67" spans="1:12">
       <c r="B67" s="9" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D67" s="5">
         <v>16</v>
@@ -6026,12 +6026,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12">
       <c r="B68" s="9" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D68" s="5">
         <v>12</v>
@@ -6061,14 +6061,14 @@
         <v>1</v>
       </c>
       <c r="L68" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12">
       <c r="B69" s="7"/>
       <c r="C69" s="7"/>
       <c r="D69" s="7" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E69" s="5">
         <f>D67*E67+D68*E68</f>
@@ -6095,9 +6095,9 @@
         <v>36</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12">
       <c r="D70" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E70" s="5">
         <f>E69-16</f>
@@ -6121,81 +6121,81 @@
       </c>
       <c r="J70" s="5"/>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12">
       <c r="D72" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="E72">
         <v>1.5</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12">
       <c r="D73" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E73">
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12">
       <c r="D74" t="s">
+        <v>56</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12">
+      <c r="D75" t="s">
+        <v>14</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12">
+      <c r="D76" t="s">
+        <v>15</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12">
+      <c r="A78" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12">
+      <c r="B79" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G79" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H79" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I79" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J79" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E74">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="D75" t="s">
-        <v>20</v>
-      </c>
-      <c r="E75">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="D76" t="s">
-        <v>21</v>
-      </c>
-      <c r="E76">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A78" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B79" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E79" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="F79" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G79" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="H79" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I79" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J79" s="4" t="s">
-        <v>3</v>
-      </c>
       <c r="L79" s="4"/>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12">
       <c r="B80" s="9" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D80" s="5">
         <v>5</v>
@@ -6225,15 +6225,15 @@
         <v>2</v>
       </c>
       <c r="L80" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="81" spans="2:12" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="81" spans="2:12">
       <c r="B81" s="9" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D81" s="5">
         <v>12</v>
@@ -6263,14 +6263,14 @@
         <v>2</v>
       </c>
       <c r="L81" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="82" spans="2:12" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="82" spans="2:12">
       <c r="B82" s="7"/>
       <c r="C82" s="7"/>
       <c r="D82" s="7" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E82" s="5">
         <f>D80*E80+D81*E81</f>
@@ -6297,9 +6297,9 @@
         <v>34</v>
       </c>
     </row>
-    <row r="83" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:12">
       <c r="D83" s="7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E83" s="5">
         <f>E82-16</f>
@@ -6323,41 +6323,41 @@
       </c>
       <c r="J83" s="5"/>
     </row>
-    <row r="85" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:12">
       <c r="D85" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="E85">
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:12">
       <c r="D86" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E86">
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:12">
       <c r="D87" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E87">
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:12">
       <c r="D88" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E88">
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:12">
       <c r="D89" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E89">
         <v>0</v>
